--- a/site/exports/tju-architecture.xlsx
+++ b/site/exports/tju-architecture.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="58.8" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>建筑学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>current_employment_status；page_last_modified；formal_dissertation_advisors；awarding_legal_entity；所有现职导航false；网页显示日期不证明最后修改时间。；canonical_bachelor_study_end；canonical_doctoral_award_year；design_authors；design_contribution_role；日期与职称差异原样保留，未自行判错或修正；阶段师承4不等于论文导师4。；来源差异/限制：英才教授；副教授；保留各来源标签；不由差异推晋升时间、现职或哪个页面已过时。；来源差异/限制：1999.9 - 2004.6；自1999-2014于天津大学建筑学院建筑学专业学习。；规范化学习止期null，明确获学士年份2004另存；不自行改原文。；来源差异/限制：2007 Graduate from Kyoto University, Graduated School, PHD；2011年毕业于日本京都大学，获建筑学博士学位；；2011，毕业于日本京都大学，建筑学博士；；明确博士获授true；规范化获授年份null，原文年份均保留，不推双博士。；来源另列创作/设计实践：名称：浙江常山中国观赏石博览馆设计；来源年份：2017；年份语义：design_practice_year_as_source_not_publication；本人角色：未知；限制：条目未列作者、团队或本人具体角色，不由人物页归属补成独立作者。；来源：https://arch.tju.edu.cn/info/1186/5721.htm；留存来源自述，不据此新增论文、任职、本人学历或当前状态认证。；来源记载职业信息：学院下属单位：建筑系。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：建筑设计、环境行为心理学、当代住宅设计原理、建筑评论；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源ID：new-recovery-tju-zhangxinnan-s002-61bac8d133d6；https://arch.tju.edu.cn/info/1186/5721.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,11 +638,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="25.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -603,7 +657,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="58.8" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -953,13 +1007,531 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>建筑学学士</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>建筑学</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1999.9为结构化时间起点；结构化止期2004.6与同页正文1999-2014冲突，规范化止期留null。获学士的明确年份2004来自独立的中文获授句，不把毕业或学习止期当授位日。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>建筑学硕士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2007-06</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>建筑设计及其理论</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>学习止期与授位日期分开；获授句仅明确2007年，没有月日。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>建筑学博士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>日本京都大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2007-10</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>建筑学</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>中文明确2011获建筑学博士，学院履历也标2011；同页教育条目英文却写2007 Graduate。保留冲突，不当作两个博士，规范化授位年份留null；学习阶段时间按结构化标签另存，非授位日期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_exchange</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>米兰理工大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2005-10</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2006-06</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原文为交换学习；非学位事件，不推该校授位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：nondegree_exchange</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_exchange</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>香港大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2004-02</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2004-07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原文为交换学习；非学位事件，不推该校授位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：nondegree_exchange</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：建筑学院</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>助教</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>京都大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2008-04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：建筑学专攻</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>常务副院长</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（单位）：建筑学院</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://arch.tju.edu.cn/info/1186/5721.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -971,18 +1543,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="18.2" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1050,8 +1622,214 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>宗本顺三</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentor</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>博士阶段</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅接受原文具体学习阶段或交换学习指导关系；不是学位论文导师或导师现职认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>张颀</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>硕士阶段</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅接受原文具体学习阶段或交换学习指导关系；不是学位论文导师或导师现职认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Kiara Molina</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>exchange_learning_guidance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>米兰理工交换学习</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅接受原文具体学习阶段或交换学习指导关系；不是学位论文导师或导师现职认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>王维仁</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>exchange_final_design_guidance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>香港大学交换学习／毕业设计</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅接受原文具体学习阶段或交换学习指导关系；不是学位论文导师或导师现职认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L5"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1062,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1074,7 +1852,7 @@
     <col width="58.8" customWidth="1" min="7" max="7"/>
     <col width="58.8" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="39.2" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1253,8 +2031,60 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>独白六法</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://arch.tju.edu.cn/info/1186/5721.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://arch.tju.edu.cn/info/1186/5721.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors：张昕楠、李飞扬、曹兆、孙德龙；来源authors_as_source：张昕楠，李飞扬，曹兆，孙德龙；来源书目信息（期）：No.187；2022（10）；来源书目信息（页码）：37-41；来源书目信息（issue_note）：原文No.187作为刊号保留，2022（10）另一期标记并列保留；不把187当卷。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1262,6 +2092,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1273,14 +2105,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43.4" customWidth="1" min="2" max="2"/>
-    <col width="58.8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1388,11 +2220,125 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-tju-zhangxinnan-s001-efa54e5d0773</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://arch.tju.edu.cn/rcpy/szdw/jzxx.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:04:25.297Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-tju-zhangxinnan-s002-61bac8d133d6</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://arch.tju.edu.cn/info/1186/5721.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:04:30.342Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张昕楠</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-tju-zhangxinnan-s003-747aa6fa53ab</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty-cn.tju.edu.cn/116132/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:04:46.362Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>tju</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>天津大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/tju-architecture.xlsx
+++ b/site/exports/tju-architecture.xlsx
@@ -1044,7 +1044,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L6" s="2" t="b">
@@ -1115,7 +1115,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="b">
